--- a/WBS_Library.xlsx
+++ b/WBS_Library.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trainings\Task 3 Library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trainings\Task 3 Library\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5E9206-D0E3-4CD4-B1A4-5913C8B52EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48AB7163-5189-4B7A-99A3-3F80157DF4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-105" windowWidth="29040" windowHeight="17505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="42">
   <si>
     <t>Task</t>
   </si>
@@ -67,43 +67,395 @@
     <t>User stories</t>
   </si>
   <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>I.I.</t>
-  </si>
-  <si>
-    <t>I.II.</t>
-  </si>
-  <si>
-    <t>I.III.</t>
-  </si>
-  <si>
-    <t>I.IV</t>
-  </si>
-  <si>
-    <t>I.V</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
     <t>Question</t>
   </si>
   <si>
     <t>Answer</t>
+  </si>
+  <si>
+    <t>Book management</t>
+  </si>
+  <si>
+    <t>Implement borrow and return book</t>
+  </si>
+  <si>
+    <t>Test book class</t>
+  </si>
+  <si>
+    <t>Implement set of test to cover the entire class</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">borrow_book() </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>method change availability status to not available</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">return_book() </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>method change availability status to available</t>
+    </r>
+  </si>
+  <si>
+    <t>User management</t>
+  </si>
+  <si>
+    <t>Create User class</t>
+  </si>
+  <si>
+    <t>Implement user methods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To be implemented functions  to see how many books are borrowed, do add and remove from borrowed list </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>get_borrowed_books()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> return borrowed books 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">add_borrowed_books() </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">adding to borrowed books </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>remove_borrowed_books()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> remove from borrrowed books
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>limit_amount_borrowed_books()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to limit how many books can be borrowed</t>
+    </r>
+  </si>
+  <si>
+    <t>To be tested all method and edge cases</t>
+  </si>
+  <si>
+    <t>Library management</t>
+  </si>
+  <si>
+    <t>Create Book base class</t>
+  </si>
+  <si>
+    <t>Create Special book class</t>
+  </si>
+  <si>
+    <t>To be created special book class</t>
+  </si>
+  <si>
+    <t>TODO</t>
+  </si>
+  <si>
+    <t>Create library classs</t>
+  </si>
+  <si>
+    <t>Implement a library class with attributes: all_books and all_users</t>
+  </si>
+  <si>
+    <t>Implement library methods</t>
+  </si>
+  <si>
+    <t>Implement functions to add new book, to register a new user, to get available books, to return all books, to return all registerd books</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">add_book()  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">adding book in library
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>register_user()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> adding new user
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">get_available_books() </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">returns list of not borrowed books
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">get_all_users() </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">retuns list of all users
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>get_all_books()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> returns list of all bookslibrary has</t>
+    </r>
+  </si>
+  <si>
+    <t>Structure setup</t>
+  </si>
+  <si>
+    <t>Create project structure</t>
+  </si>
+  <si>
+    <t>Implementation of book class with all attributes  as title, author, category and availability status</t>
+  </si>
+  <si>
+    <t>Docstring 
+Private attributes</t>
+  </si>
+  <si>
+    <t>To be implemented functions controlling borrowing and returning books</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test create a book with valid / invalid data
+Test borrow and return </t>
+  </si>
+  <si>
+    <t>Implement a User class with attributes: Name, borrowed book</t>
+  </si>
+  <si>
+    <t>To create folders and additional files required for the project</t>
+  </si>
+  <si>
+    <t>To have structure with all folders as src/test/coverаge
+To have setup for venv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -154,6 +506,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -181,7 +540,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -256,29 +615,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -288,34 +655,109 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -331,10 +773,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -600,7 +1038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" customWidth="1"/>
@@ -615,469 +1053,544 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="29" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+    <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="20"/>
+      <c r="B2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="C2" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="30"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="D3" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="31"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+    </row>
+    <row r="4" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="30"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="31"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+    </row>
+    <row r="5" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="D5" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15" t="s">
+      <c r="E5" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="31"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+    </row>
+    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="20"/>
+      <c r="B6" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+    </row>
+    <row r="7" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="A7" s="20"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="20"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+    </row>
+    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="20"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+    </row>
+    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="20"/>
+      <c r="B9" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10" spans="1:9" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+    </row>
+    <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
+      <c r="A13" s="1"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
       <c r="E23" s="11"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="10"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
+      <c r="A27" s="4"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B9:B11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1093,88 +1606,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>18</v>
+      <c r="A1" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
